--- a/model_maker_web_v2/results/Senergy/Senergy_stage1.xlsx
+++ b/model_maker_web_v2/results/Senergy/Senergy_stage1.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Senergy Modbus Protocol-Korea-V1.2.4.pdf</t>
+          <t>Senergy Modbus Protocol Map(260402).xlsx</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:58</t>
+          <t>2026-04-03 16:03</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -756,44 +756,28 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>INNER_TEMP</t>
+          <t>Flash / Update (펌웨어 업데이트 중)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>0x101C</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0006</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>°C 1</t>
-        </is>
-      </c>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Inner Temperature</t>
-        </is>
-      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -801,27 +785,23 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Total Energy</t>
+          <t>INNER_TEMP</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0x1021</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x101C</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>kWh</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -831,10 +811,14 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Inner Temperature</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -842,31 +826,35 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Total generation time</t>
+          <t>Total Energy</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>0x1023</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1021</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>U32</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -875,22 +863,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Decimals of total energy</t>
+          <t>Total generation time</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>0x104C</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1023</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
@@ -899,16 +883,8 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>cumulative_energy_low</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Wh</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -916,34 +892,38 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Device Model name</t>
+          <t>Decimals of total energy</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>0x1A00</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x104C</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Wh</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>cumulative_energy_low</t>
+        </is>
+      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Ex.：PV 30KTL</t>
+          <t>Relate to 0x1021, if total energy is 220.836kWh, then 0x104C is 836Wh</t>
         </is>
       </c>
     </row>
@@ -953,19 +933,15 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Device Serial number</t>
+          <t>Device Model name</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>0x1A10</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A00</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>STRINGING</t>
@@ -980,7 +956,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1234-123456789</t>
+          <t>Ex.：PV 30KTL</t>
         </is>
       </c>
     </row>
@@ -990,19 +966,15 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Master firmware version</t>
+          <t>Device Serial number</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>0x1A1C</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A10</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>STRINGING</t>
@@ -1017,7 +989,7 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Ex.：123456</t>
+          <t>Ex.：1234-123456789</t>
         </is>
       </c>
     </row>
@@ -1027,19 +999,15 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Slave firmware version</t>
+          <t>Master firmware version</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>0x1A26</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A1C</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>STRINGING</t>
@@ -1064,22 +1032,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>MPPT_COUNT</t>
+          <t>Slave firmware version</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>0x1A3B</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A26</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>STRINGING</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -1091,7 +1055,7 @@
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>MPPT Number | Ex.：1=1 MPPT</t>
+          <t>Ex.：123456</t>
         </is>
       </c>
     </row>
@@ -1101,19 +1065,15 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nominal Voltage</t>
+          <t>MPPT_COUNT</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>0x1A44</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A3B</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1128,7 +1088,7 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Ex.：2200 = 220V</t>
+          <t>MPPT Number | Ex.：1=1 MPPT</t>
         </is>
       </c>
     </row>
@@ -1138,25 +1098,25 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Nominal Frequency</t>
+          <t>Nominal Voltage</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>0x1A45</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A44</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1165,7 +1125,7 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Ex.：5000 = 50Hz</t>
+          <t>Ex.：2200 = 220VFor CN (NB/T 32004) regulation code (0x5101=0x0E), the unit is 10ms. Other regulation codes use 1ms.</t>
         </is>
       </c>
     </row>
@@ -1175,19 +1135,15 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nominal Active Power(Low word)</t>
+          <t>Nominal Frequency</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>0x1A46</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A45</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1195,7 +1151,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -1206,7 +1162,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1500 = 1500W</t>
+          <t>Ex.：5000 = 50HzOnly support for 3 phase model (0x1A48 = 3).</t>
         </is>
       </c>
     </row>
@@ -1216,25 +1172,25 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Grid Phase Number</t>
+          <t>Nominal Active Power (Low word)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>0x1A48</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A46</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>W 1</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1243,7 +1199,7 @@
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>1=single phase2=split phase3=three phases</t>
+          <t>Ex.：1500 = 1500W</t>
         </is>
       </c>
     </row>
@@ -1253,29 +1209,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nominal Active Power(High word)</t>
+          <t>Grid Phase Number</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>0x1A4E</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A48</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>W 1</t>
-        </is>
-      </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1284,7 +1232,7 @@
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Ex.：1 = (1*65536)W</t>
+          <t>1=single phase2=split phase3=three phases</t>
         </is>
       </c>
     </row>
@@ -1294,25 +1242,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>EMS Firmware Version</t>
+          <t>Nominal Active Power (High word)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>0x1A60</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A4E</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>W 1</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>RO</t>
@@ -1321,7 +1269,7 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Ex.：123456</t>
+          <t>Ex.：1 = (1*65536)W</t>
         </is>
       </c>
     </row>
@@ -1331,19 +1279,15 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>LCD firmware version</t>
+          <t>EMS Firmware Version</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>0x1A8E</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1A60</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>STRINGING</t>
@@ -1362,120 +1306,108 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>LCD firmware version</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0x1A8E</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>STRINGING</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Ex.：123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>STATUS 레지스터</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>FC</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Unit/Scale</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>R/W</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>H01 Field</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Inverter Mode</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>0x101D</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>inverter_status</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Inverter Mode Table</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>DER-AVM digital meterconnect status</t>
+          <t>Off-Grid (독립 운전)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>0x1210</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0004</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="6" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1492,23 +1424,19 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>DER-AVM mode</t>
+          <t>Derating (출력 제한 운전 중)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>0x1211</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0007</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="6" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1517,221 +1445,213 @@
       <c r="F44" s="6" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Shutdown mode</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>0x0009</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Inverter Mode</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>0x101D</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>inverter_status</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Inverter Mode Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>DER-AVM digital meter connect status</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>0x1210</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>0: disconnected1: connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>DER-AVM mode</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>0x1211</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>0: self control1: DER-AVM control</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>ALARM 레지스터</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>FC</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>Unit/Scale</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>R/W</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>H01 Field</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>GFCI abnormal</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>0x0004</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr"/>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Internal communication error</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>0x000A</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Internal storage error</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>0x000C</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Inverter abnormal</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>0x000E</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Boost abnormal</t>
+          <t>Fault / Alarm (고장 발생)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>0x000F</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0005</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
       <c r="E53" s="7" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1748,7 +1668,7 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
@@ -1760,11 +1680,7 @@
           <t>0x101E</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="inlineStr"/>
       <c r="E54" s="7" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1789,7 +1705,7 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
@@ -1801,11 +1717,7 @@
           <t>0x101F</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="7" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1830,7 +1742,7 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
@@ -1842,11 +1754,7 @@
           <t>0x1020</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="inlineStr"/>
       <c r="E56" s="7" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1871,7 +1779,7 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
@@ -1883,11 +1791,7 @@
           <t>0x6006</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="inlineStr"/>
       <c r="E57" s="7" t="inlineStr">
         <is>
           <t>U16</t>
@@ -1900,7 +1804,11 @@
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>[0, 1]0: EEPROM setting NOT to default1: EEPROM setting to default</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2591,7 +2499,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Accumulated energy ofimport</t>
+          <t>Accumulated energy of import</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2645,7 +2553,11 @@
           <t>U16</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Wh</t>
+        </is>
+      </c>
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr"/>
     </row>
@@ -2687,7 +2599,7 @@
       <c r="I18" s="11" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>6=PV6 fuse open d, 7=PV7 fuse open d, 8=PV8 fuse open d</t>
+          <t>1=L1 Voltage, 10=L3 Current, 11=L3 Power, 12=L3 Frequency, 13=MPPT1 Voltage, 14=MPPT1 Current... (+28)</t>
         </is>
       </c>
     </row>
@@ -2727,11 +2639,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr"/>
       <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>0=Inverter over d, 1=Inverter relay , 2=Remote off, 3=Inverter over t, 4=GFCI abnormal, 5=PV string rever... (+10)</t>
-        </is>
-      </c>
+      <c r="J19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -2769,11 +2677,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>136=String 1-2 curr, 137=String 1-3 curr, 138=String 1-4 curr, 139=Tracker 2 volta, 140=String 2-1 curr, 141=String 2-2 curr... (+33)</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -4756,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -6861,7 +6765,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MONITORING 전체 (180개)</t>
+          <t>MONITORING 전체 (185개)</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6817,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Broadcast address</t>
+          <t>Wait / Initial (대기/초기화)</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -6921,11 +6825,7 @@
           <t>0x0000</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D60" s="9" t="inlineStr"/>
       <c r="E60" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -6945,7 +6845,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Start bit</t>
+          <t>Standby (스탠바이)</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -6953,11 +6853,7 @@
           <t>0x0001</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D61" s="9" t="inlineStr"/>
       <c r="E61" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -6977,7 +6873,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Register number</t>
+          <t>Initialization (초기화 중)</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -6985,11 +6881,7 @@
           <t>0x0002</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D62" s="9" t="inlineStr"/>
       <c r="E62" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7009,7 +6901,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Read register address</t>
+          <t>On-Grid / Normal (정상 발전 / 계통 연계)</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -7017,11 +6909,7 @@
           <t>0x0003</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="D63" s="9" t="inlineStr"/>
       <c r="E63" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7041,22 +6929,18 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>PV string reverse</t>
+          <t>Grid over current, [0,1]</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>0x0005</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0008</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr"/>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -7073,19 +6957,15 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>0x07</t>
+          <t>EN50438 (유럽 공통)</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>0x0007</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7105,19 +6985,15 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Dc-link over voltage</t>
+          <t>Self control(outage), [0,1]</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>0x0009</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x000B</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr"/>
       <c r="E66" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7137,19 +7013,15 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Software incompatibility</t>
+          <t>Leakage current abnormal, [0,1]</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>0x000B</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x000C</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr"/>
       <c r="E67" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7169,19 +7041,15 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Data inconsistency</t>
+          <t>Register value</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>0x000D</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x0026</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr"/>
       <c r="E68" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7201,31 +7069,35 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Byte number</t>
+          <t>L1 Voltage</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>0x0026</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1001</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr"/>
       <c r="E69" s="9" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr"/>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>r_voltage</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n">
@@ -7233,19 +7105,15 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>L1 Voltage</t>
+          <t>L1 Current</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>0x1001</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1002</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr"/>
       <c r="E70" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7253,7 +7121,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -7263,7 +7131,7 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>r_voltage</t>
+          <t>r_current</t>
         </is>
       </c>
     </row>
@@ -7273,27 +7141,23 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>L1 Current</t>
+          <t>L1 Power</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>0x1002</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1003</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr"/>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -7301,11 +7165,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>r_current</t>
-        </is>
-      </c>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -7313,27 +7173,23 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>L1 Power</t>
+          <t>L1 Frequency</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>0x1003</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1005</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr"/>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -7341,7 +7197,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr"/>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
@@ -7349,19 +7209,15 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>L1 Frequency</t>
+          <t>L2 Voltage</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>0x1005</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1006</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr"/>
       <c r="E73" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7369,7 +7225,7 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Hz 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
@@ -7379,7 +7235,7 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>s_voltage</t>
         </is>
       </c>
     </row>
@@ -7389,19 +7245,15 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>L2 Voltage</t>
+          <t>L2 Current</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>0x1006</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1007</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr"/>
       <c r="E74" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7409,7 +7261,7 @@
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
@@ -7419,7 +7271,7 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>s_voltage</t>
+          <t>s_current</t>
         </is>
       </c>
     </row>
@@ -7429,27 +7281,23 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>L2 Current</t>
+          <t>L2 Power</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>0x1007</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1008</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr"/>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -7457,11 +7305,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>s_current</t>
-        </is>
-      </c>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
@@ -7469,27 +7313,23 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>L2 Power</t>
+          <t>L2 Frequency</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>0x1008</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x100A</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr"/>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -7497,7 +7337,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -7505,19 +7349,15 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>L2 Frequency</t>
+          <t>L3 Voltage</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>0x100A</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x100B</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7525,7 +7365,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Hz 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -7535,7 +7375,7 @@
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>t_voltage</t>
         </is>
       </c>
     </row>
@@ -7545,19 +7385,15 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>L3 Voltage</t>
+          <t>L3 Current</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>0x100B</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x100C</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr"/>
       <c r="E78" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7565,7 +7401,7 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
@@ -7575,7 +7411,7 @@
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>t_voltage</t>
+          <t>t_current</t>
         </is>
       </c>
     </row>
@@ -7585,27 +7421,23 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>L3 Current</t>
+          <t>L3 Power</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>0x100C</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x100D</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -7613,11 +7445,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>t_current</t>
-        </is>
-      </c>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
@@ -7625,27 +7453,23 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>L3 Power</t>
+          <t>L3 Frequency</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>0x100D</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x100F</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr"/>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -7653,7 +7477,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -7661,19 +7489,15 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>L3 Frequency</t>
+          <t>MPPT1 Voltage</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>0x100F</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1010</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr"/>
       <c r="E81" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -7681,7 +7505,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Hz 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -7691,7 +7515,7 @@
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>mppt1_voltage</t>
         </is>
       </c>
     </row>
@@ -7701,27 +7525,23 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>MPPT1 Voltage</t>
+          <t>MPPT1 Current</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>0x1010</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1011</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr"/>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
@@ -7731,7 +7551,7 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>mppt1_voltage</t>
+          <t>mppt1_current</t>
         </is>
       </c>
     </row>
@@ -7741,27 +7561,23 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>MPPT1 Current</t>
+          <t>MPPT1 Power</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>0x1011</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1012</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr"/>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
@@ -7771,7 +7587,7 @@
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>mppt1_current</t>
+          <t>mppt1_power</t>
         </is>
       </c>
     </row>
@@ -7781,27 +7597,23 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>MPPT1 Power</t>
+          <t>MPPT2 Voltage</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>0x1012</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1014</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr"/>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
@@ -7811,7 +7623,7 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>mppt1_power</t>
+          <t>mppt2_voltage</t>
         </is>
       </c>
     </row>
@@ -7821,27 +7633,23 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>MPPT2 Voltage</t>
+          <t>MPPT2 Current</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>0x1014</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1015</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr"/>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -7851,7 +7659,7 @@
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>mppt2_voltage</t>
+          <t>mppt2_current</t>
         </is>
       </c>
     </row>
@@ -7861,27 +7669,23 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>MPPT2 Current</t>
+          <t>MPPT2 Power</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>0x1015</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1016</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr"/>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
@@ -7891,7 +7695,7 @@
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>mppt2_current</t>
+          <t>mppt2_power</t>
         </is>
       </c>
     </row>
@@ -7901,27 +7705,23 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>MPPT2 Power</t>
+          <t>MPPT3 Voltage</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>0x1016</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1018</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr"/>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
@@ -7931,7 +7731,7 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>mppt2_power</t>
+          <t>mppt3_voltage</t>
         </is>
       </c>
     </row>
@@ -7941,27 +7741,23 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>MPPT3 Voltage</t>
+          <t>MPPT3 Current</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>0x1018</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1019</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr"/>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
@@ -7971,7 +7767,7 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>mppt3_voltage</t>
+          <t>mppt3_current</t>
         </is>
       </c>
     </row>
@@ -7981,27 +7777,23 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>MPPT3 Current</t>
+          <t>MPPT3 Power</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>0x1019</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x101A</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr"/>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -8011,7 +7803,7 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>mppt3_current</t>
+          <t>mppt3_power</t>
         </is>
       </c>
     </row>
@@ -8021,19 +7813,15 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>MPPT3 Power</t>
+          <t>DAILY_ENERGY</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>0x101A</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1027</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr"/>
       <c r="E90" s="9" t="inlineStr">
         <is>
           <t>U32</t>
@@ -8041,7 +7829,7 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>Wh</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
@@ -8051,7 +7839,7 @@
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>mppt3_power</t>
+          <t>daily_energy</t>
         </is>
       </c>
     </row>
@@ -8061,27 +7849,23 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>DAILY_ENERGY</t>
+          <t>Grid total Active Power</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>0x1027</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1037</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr"/>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Wh</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -8091,7 +7875,7 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>daily_energy</t>
+          <t>ac_power</t>
         </is>
       </c>
     </row>
@@ -8101,19 +7885,15 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Grid total Active Power</t>
+          <t>Grid total Reactive Power</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>0x1037</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1039</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr"/>
       <c r="E92" s="9" t="inlineStr">
         <is>
           <t>S32</t>
@@ -8121,7 +7901,7 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
@@ -8141,35 +7921,31 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Grid total Reactive Power</t>
+          <t>PV Today Peak Power</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>0x1039</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x103B</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr">
         <is>
           <t>S32</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr"/>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>W 0.1</t>
+        </is>
+      </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>ac_power</t>
-        </is>
-      </c>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="n">
@@ -8177,27 +7953,23 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>PV Today Peak Power</t>
+          <t>Power Factor</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>0x103B</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x103D</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr"/>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -8205,7 +7977,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>power_factor</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
@@ -8213,25 +7989,25 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Power Factor</t>
+          <t>MPPT4 Voltage</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>0x103D</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x103E</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr"/>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
           <t>RO</t>
@@ -8239,7 +8015,7 @@
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>power_factor</t>
+          <t>mppt4_voltage</t>
         </is>
       </c>
     </row>
@@ -8249,27 +8025,23 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>MPPT4 Voltage</t>
+          <t>MPPT4 Current</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>0x103E</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x103F</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
@@ -8279,7 +8051,7 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>mppt4_voltage</t>
+          <t>mppt4_current</t>
         </is>
       </c>
     </row>
@@ -8289,27 +8061,23 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>MPPT4 Current</t>
+          <t>MPPT4 Power</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>0x103F</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1040</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr"/>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
@@ -8319,7 +8087,7 @@
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>mppt4_current</t>
+          <t>mppt4_power</t>
         </is>
       </c>
     </row>
@@ -8329,19 +8097,15 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>MPPT4 Power</t>
+          <t>PV total input power</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>0x1040</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1048</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr"/>
       <c r="E98" s="9" t="inlineStr">
         <is>
           <t>U32</t>
@@ -8359,7 +8123,7 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>mppt4_power</t>
+          <t>pv_power</t>
         </is>
       </c>
     </row>
@@ -8369,27 +8133,23 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>PV total input power</t>
+          <t>String1 input voltage</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>0x1048</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1050</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr"/>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
@@ -8399,7 +8159,7 @@
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>pv_power</t>
+          <t>string1_voltage</t>
         </is>
       </c>
     </row>
@@ -8409,27 +8169,23 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>String1 input voltage</t>
+          <t>String1 input current</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>0x1050</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1051</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
@@ -8439,7 +8195,7 @@
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>string1_voltage</t>
+          <t>string1_current</t>
         </is>
       </c>
     </row>
@@ -8449,27 +8205,23 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>String1 input current</t>
+          <t>String2 input voltage</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>0x1051</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1052</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr"/>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
@@ -8479,7 +8231,7 @@
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>string1_current</t>
+          <t>string2_voltage</t>
         </is>
       </c>
     </row>
@@ -8489,27 +8241,23 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>String2 input voltage</t>
+          <t>String2 input current</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>0x1052</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1053</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr"/>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
@@ -8519,7 +8267,7 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>string2_voltage</t>
+          <t>string2_current</t>
         </is>
       </c>
     </row>
@@ -8529,27 +8277,23 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>String2 input current</t>
+          <t>String3 input voltage</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>0x1053</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1054</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr"/>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
@@ -8559,7 +8303,7 @@
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>string2_current</t>
+          <t>string3_voltage</t>
         </is>
       </c>
     </row>
@@ -8569,27 +8313,23 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>String3 input voltage</t>
+          <t>String3 input current</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>0x1054</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1055</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr"/>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
@@ -8599,7 +8339,7 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>string3_voltage</t>
+          <t>string3_current</t>
         </is>
       </c>
     </row>
@@ -8609,27 +8349,23 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>String3 input current</t>
+          <t>String4 input voltage</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>0x1055</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1056</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr"/>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G105" s="9" t="inlineStr">
@@ -8639,7 +8375,7 @@
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>string3_current</t>
+          <t>string4_voltage</t>
         </is>
       </c>
     </row>
@@ -8649,27 +8385,23 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>String4 input voltage</t>
+          <t>String4 input current</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>0x1056</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1057</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr"/>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -8679,7 +8411,7 @@
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>string4_voltage</t>
+          <t>string4_current</t>
         </is>
       </c>
     </row>
@@ -8689,27 +8421,23 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>String4 input current</t>
+          <t>String5 input voltage</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>0x1057</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1058</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
@@ -8719,7 +8447,7 @@
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>string4_current</t>
+          <t>string5_voltage</t>
         </is>
       </c>
     </row>
@@ -8729,27 +8457,23 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>String5 input voltage</t>
+          <t>String5 input current</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>0x1058</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1059</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr"/>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
@@ -8759,7 +8483,7 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>string5_voltage</t>
+          <t>string5_current</t>
         </is>
       </c>
     </row>
@@ -8769,27 +8493,23 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>String5 input current</t>
+          <t>String6 input voltage</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>0x1059</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105A</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
@@ -8799,7 +8519,7 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>string5_current</t>
+          <t>string6_voltage</t>
         </is>
       </c>
     </row>
@@ -8809,27 +8529,23 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>String6 input voltage</t>
+          <t>String6 input current</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>0x105A</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105B</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr"/>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
@@ -8839,7 +8555,7 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>string6_voltage</t>
+          <t>string6_current</t>
         </is>
       </c>
     </row>
@@ -8849,27 +8565,23 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>String6 input current</t>
+          <t>String7 input voltage</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>0x105B</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105C</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr"/>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G111" s="9" t="inlineStr">
@@ -8879,7 +8591,7 @@
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>string6_current</t>
+          <t>string7_voltage</t>
         </is>
       </c>
     </row>
@@ -8889,27 +8601,23 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>String7 input voltage</t>
+          <t>String7 input current</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>0x105C</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105D</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr"/>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
@@ -8919,7 +8627,7 @@
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>string7_voltage</t>
+          <t>string7_current</t>
         </is>
       </c>
     </row>
@@ -8929,27 +8637,23 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>String7 input current</t>
+          <t>String8 input voltage</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>0x105D</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105E</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr"/>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
@@ -8959,7 +8663,7 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>string7_current</t>
+          <t>string8_voltage</t>
         </is>
       </c>
     </row>
@@ -8969,27 +8673,23 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>String8 input voltage</t>
+          <t>String8 input current</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>0x105E</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x105F</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr"/>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
@@ -8999,7 +8699,7 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>string8_voltage</t>
+          <t>string8_current</t>
         </is>
       </c>
     </row>
@@ -9009,27 +8709,23 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>String8 input current</t>
+          <t>String9 input voltage</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>0x105F</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1060</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr"/>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
@@ -9039,7 +8735,7 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>string8_current</t>
+          <t>string9_voltage</t>
         </is>
       </c>
     </row>
@@ -9049,27 +8745,23 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>String9 input voltage</t>
+          <t>String9 input current</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>0x1060</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1061</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr"/>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
@@ -9079,7 +8771,7 @@
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>string9_voltage</t>
+          <t>string9_current</t>
         </is>
       </c>
     </row>
@@ -9089,27 +8781,23 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>String9 input current</t>
+          <t>String10 input voltage</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>0x1061</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1062</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr"/>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
@@ -9119,7 +8807,7 @@
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>string9_current</t>
+          <t>string10_voltage</t>
         </is>
       </c>
     </row>
@@ -9129,27 +8817,23 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>String10 input voltage</t>
+          <t>String10 input current</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>0x1062</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1063</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr"/>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
@@ -9159,7 +8843,7 @@
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>string10_voltage</t>
+          <t>string10_current</t>
         </is>
       </c>
     </row>
@@ -9169,27 +8853,23 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>String10 input current</t>
+          <t>String11 input voltage</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>0x1063</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1064</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr"/>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
@@ -9199,7 +8879,7 @@
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>string10_current</t>
+          <t>string11_voltage</t>
         </is>
       </c>
     </row>
@@ -9209,27 +8889,23 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>String11 input voltage</t>
+          <t>String11 input current</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>0x1064</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1065</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr"/>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
@@ -9239,7 +8915,7 @@
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>string11_voltage</t>
+          <t>string11_current</t>
         </is>
       </c>
     </row>
@@ -9249,27 +8925,23 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>String11 input current</t>
+          <t>String12 input voltage</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>0x1065</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1066</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr"/>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
@@ -9279,7 +8951,7 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>string11_current</t>
+          <t>string12_voltage</t>
         </is>
       </c>
     </row>
@@ -9289,27 +8961,23 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>String12 input voltage</t>
+          <t>String12 input current</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>0x1066</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1067</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr"/>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
@@ -9319,7 +8987,7 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>string12_voltage</t>
+          <t>string12_current</t>
         </is>
       </c>
     </row>
@@ -9329,27 +8997,23 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>String12 input current</t>
+          <t>String13 input voltage</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>0x1067</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1068</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr"/>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
@@ -9359,7 +9023,7 @@
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>string12_current</t>
+          <t>string13_voltage</t>
         </is>
       </c>
     </row>
@@ -9369,27 +9033,23 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>String13 input voltage</t>
+          <t>String13 input current</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>0x1068</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1069</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr"/>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
@@ -9399,7 +9059,7 @@
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>string13_voltage</t>
+          <t>string13_current</t>
         </is>
       </c>
     </row>
@@ -9409,27 +9069,23 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>String13 input current</t>
+          <t>String14 input voltage</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>0x1069</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106A</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr"/>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
@@ -9439,7 +9095,7 @@
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>string13_current</t>
+          <t>string14_voltage</t>
         </is>
       </c>
     </row>
@@ -9449,27 +9105,23 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>String14 input voltage</t>
+          <t>String14 input current</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>0x106A</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106B</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr"/>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
@@ -9479,7 +9131,7 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>string14_voltage</t>
+          <t>string14_current</t>
         </is>
       </c>
     </row>
@@ -9489,27 +9141,23 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>String14 input current</t>
+          <t>String15 input voltage</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>0x106B</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106C</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr"/>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
@@ -9519,7 +9167,7 @@
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
-          <t>string14_current</t>
+          <t>string15_voltage</t>
         </is>
       </c>
     </row>
@@ -9529,27 +9177,23 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>String15 input voltage</t>
+          <t>String15 input current</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>0x106C</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106D</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr"/>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
@@ -9559,7 +9203,7 @@
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>string15_voltage</t>
+          <t>string15_current</t>
         </is>
       </c>
     </row>
@@ -9569,27 +9213,23 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>String15 input current</t>
+          <t>String16 input voltage</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>0x106D</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106E</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr"/>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
@@ -9599,7 +9239,7 @@
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>string15_current</t>
+          <t>string16_voltage</t>
         </is>
       </c>
     </row>
@@ -9609,27 +9249,23 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>String16 input voltage</t>
+          <t>String16 input current</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>0x106E</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x106F</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr"/>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
@@ -9639,7 +9275,7 @@
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>string16_voltage</t>
+          <t>string16_current</t>
         </is>
       </c>
     </row>
@@ -9649,27 +9285,23 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>String16 input current</t>
+          <t>String17 input voltage</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>0x106F</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1070</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr"/>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
@@ -9679,7 +9311,7 @@
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>string16_current</t>
+          <t>string17_voltage</t>
         </is>
       </c>
     </row>
@@ -9689,27 +9321,23 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>String17 input voltage</t>
+          <t>String17 input current</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>0x1070</t>
-        </is>
-      </c>
-      <c r="D132" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1071</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr"/>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G132" s="9" t="inlineStr">
@@ -9719,7 +9347,7 @@
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>string17_voltage</t>
+          <t>string17_current</t>
         </is>
       </c>
     </row>
@@ -9729,27 +9357,23 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>String17 input current</t>
+          <t>String18 input voltage</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>0x1071</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1072</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr"/>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
@@ -9759,7 +9383,7 @@
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>string17_current</t>
+          <t>string18_voltage</t>
         </is>
       </c>
     </row>
@@ -9769,27 +9393,23 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>String18 input voltage</t>
+          <t>String18 input current</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>0x1072</t>
-        </is>
-      </c>
-      <c r="D134" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1073</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr"/>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
@@ -9799,7 +9419,7 @@
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>string18_voltage</t>
+          <t>string18_current</t>
         </is>
       </c>
     </row>
@@ -9809,27 +9429,23 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>String18 input current</t>
+          <t>String19 input voltage</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>0x1073</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1074</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr"/>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
@@ -9839,7 +9455,7 @@
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>string18_current</t>
+          <t>string19_voltage</t>
         </is>
       </c>
     </row>
@@ -9849,27 +9465,23 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>String19 input voltage</t>
+          <t>String19 input current</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>0x1074</t>
-        </is>
-      </c>
-      <c r="D136" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1075</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr"/>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G136" s="9" t="inlineStr">
@@ -9879,7 +9491,7 @@
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>string19_voltage</t>
+          <t>string19_current</t>
         </is>
       </c>
     </row>
@@ -9889,27 +9501,23 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>String19 input current</t>
+          <t>String20 input voltage</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>0x1075</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1076</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr"/>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
@@ -9919,7 +9527,7 @@
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>string19_current</t>
+          <t>string20_voltage</t>
         </is>
       </c>
     </row>
@@ -9929,27 +9537,23 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>String20 input voltage</t>
+          <t>String20 input current</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>0x1076</t>
-        </is>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1077</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr"/>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
@@ -9959,7 +9563,7 @@
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>string20_voltage</t>
+          <t>string20_current</t>
         </is>
       </c>
     </row>
@@ -9969,27 +9573,23 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>String20 input current</t>
+          <t>String21 input voltage</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>0x1077</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1078</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr"/>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
@@ -9999,7 +9599,7 @@
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>string20_current</t>
+          <t>string21_voltage</t>
         </is>
       </c>
     </row>
@@ -10009,27 +9609,23 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>String21 input voltage</t>
+          <t>String21 input current</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>0x1078</t>
-        </is>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1079</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr"/>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
@@ -10039,7 +9635,7 @@
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>string21_voltage</t>
+          <t>string21_current</t>
         </is>
       </c>
     </row>
@@ -10049,27 +9645,23 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>String21 input current</t>
+          <t>String22 input voltage</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>0x1079</t>
-        </is>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107A</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr"/>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
@@ -10079,7 +9671,7 @@
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>string21_current</t>
+          <t>string22_voltage</t>
         </is>
       </c>
     </row>
@@ -10089,27 +9681,23 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>String22 input voltage</t>
+          <t>String22 input current</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>0x107A</t>
-        </is>
-      </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107B</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr"/>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
@@ -10119,7 +9707,7 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>string22_voltage</t>
+          <t>string22_current</t>
         </is>
       </c>
     </row>
@@ -10129,27 +9717,23 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>String22 input current</t>
+          <t>String23 input voltage</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>0x107B</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107C</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr"/>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G143" s="9" t="inlineStr">
@@ -10159,7 +9743,7 @@
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
-          <t>string22_current</t>
+          <t>string23_voltage</t>
         </is>
       </c>
     </row>
@@ -10169,27 +9753,23 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>String23 input voltage</t>
+          <t>String23 input current</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>0x107C</t>
-        </is>
-      </c>
-      <c r="D144" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107D</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr"/>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
@@ -10199,7 +9779,7 @@
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>string23_voltage</t>
+          <t>string23_current</t>
         </is>
       </c>
     </row>
@@ -10209,27 +9789,23 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>String23 input current</t>
+          <t>String24 input voltage</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>0x107D</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107E</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr"/>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
@@ -10239,7 +9815,7 @@
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>string23_current</t>
+          <t>string24_voltage</t>
         </is>
       </c>
     </row>
@@ -10249,27 +9825,23 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>String24 input voltage</t>
+          <t>String24 input current</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>0x107E</t>
-        </is>
-      </c>
-      <c r="D146" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x107F</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr"/>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
@@ -10279,7 +9851,7 @@
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>string24_voltage</t>
+          <t>string24_current</t>
         </is>
       </c>
     </row>
@@ -10289,27 +9861,23 @@
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>String24 input current</t>
+          <t>MPPT5 Voltage</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>0x107F</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1080</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr"/>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
@@ -10319,7 +9887,7 @@
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
-          <t>string24_current</t>
+          <t>mppt5_voltage</t>
         </is>
       </c>
     </row>
@@ -10329,27 +9897,23 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>MPPT5 Voltage</t>
+          <t>MPPT5 Current</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>0x1080</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1081</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr"/>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
@@ -10359,7 +9923,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>mppt5_voltage</t>
+          <t>mppt5_current</t>
         </is>
       </c>
     </row>
@@ -10369,27 +9933,23 @@
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>MPPT5 Current</t>
+          <t>MPPT5 Power</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>0x1081</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1082</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr"/>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
@@ -10399,7 +9959,7 @@
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>mppt5_current</t>
+          <t>mppt5_power</t>
         </is>
       </c>
     </row>
@@ -10409,27 +9969,23 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>MPPT5 Power</t>
+          <t>MPPT6 Voltage</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>0x1082</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1084</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr"/>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
@@ -10439,7 +9995,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>mppt5_power</t>
+          <t>mppt6_voltage</t>
         </is>
       </c>
     </row>
@@ -10449,27 +10005,23 @@
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>MPPT6 Voltage</t>
+          <t>MPPT6 Current</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>0x1084</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1085</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr"/>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
@@ -10479,7 +10031,7 @@
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>mppt6_voltage</t>
+          <t>mppt6_current</t>
         </is>
       </c>
     </row>
@@ -10489,27 +10041,23 @@
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>MPPT6 Current</t>
+          <t>MPPT6 Power</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>0x1085</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1086</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr"/>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G152" s="9" t="inlineStr">
@@ -10519,7 +10067,7 @@
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>mppt6_current</t>
+          <t>mppt6_power</t>
         </is>
       </c>
     </row>
@@ -10529,27 +10077,23 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>MPPT6 Power</t>
+          <t>MPPT7 Voltage</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>0x1086</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1088</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr"/>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
@@ -10559,7 +10103,7 @@
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>mppt6_power</t>
+          <t>mppt7_voltage</t>
         </is>
       </c>
     </row>
@@ -10569,27 +10113,23 @@
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>MPPT7 Voltage</t>
+          <t>MPPT7 Current</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>0x1088</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1089</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr"/>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
@@ -10599,7 +10139,7 @@
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>mppt7_voltage</t>
+          <t>mppt7_current</t>
         </is>
       </c>
     </row>
@@ -10609,27 +10149,23 @@
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>MPPT7 Current</t>
+          <t>MPPT7 Power</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>0x1089</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x108A</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr"/>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
@@ -10639,7 +10175,7 @@
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
-          <t>mppt7_current</t>
+          <t>mppt7_power</t>
         </is>
       </c>
     </row>
@@ -10649,27 +10185,23 @@
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>MPPT7 Power</t>
+          <t>MPPT8 Voltage</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>0x108A</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x108C</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr"/>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
@@ -10679,7 +10211,7 @@
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>mppt7_power</t>
+          <t>mppt8_voltage</t>
         </is>
       </c>
     </row>
@@ -10689,27 +10221,23 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>MPPT8 Voltage</t>
+          <t>MPPT8 Current</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>0x108C</t>
-        </is>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x108D</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr"/>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
@@ -10719,7 +10247,7 @@
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>mppt8_voltage</t>
+          <t>mppt8_current</t>
         </is>
       </c>
     </row>
@@ -10729,27 +10257,23 @@
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>MPPT8 Current</t>
+          <t>MPPT8 Power</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>0x108D</t>
-        </is>
-      </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x108E</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr"/>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
@@ -10759,7 +10283,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>mppt8_current</t>
+          <t>mppt8_power</t>
         </is>
       </c>
     </row>
@@ -10769,27 +10293,23 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>MPPT8 Power</t>
+          <t>MPPT9 Voltage</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>0x108E</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1090</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr"/>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
@@ -10799,7 +10319,7 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>mppt8_power</t>
+          <t>mppt9_voltage</t>
         </is>
       </c>
     </row>
@@ -10809,27 +10329,23 @@
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>MPPT9 Voltage</t>
+          <t>MPPT9 Current</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>0x1090</t>
-        </is>
-      </c>
-      <c r="D160" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1091</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr"/>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
@@ -10839,7 +10355,7 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>mppt9_voltage</t>
+          <t>mppt9_current</t>
         </is>
       </c>
     </row>
@@ -10849,27 +10365,23 @@
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>MPPT9 Current</t>
+          <t>MPPT9 Power</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>0x1091</t>
-        </is>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1092</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr"/>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
@@ -10879,7 +10391,7 @@
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
-          <t>mppt9_current</t>
+          <t>mppt9_power</t>
         </is>
       </c>
     </row>
@@ -10889,27 +10401,23 @@
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>MPPT9 Power</t>
+          <t>External fan speed duty percentage</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>0x1092</t>
-        </is>
-      </c>
-      <c r="D162" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x120C</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr"/>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -10917,11 +10425,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H162" s="9" t="inlineStr">
-        <is>
-          <t>mppt9_power</t>
-        </is>
-      </c>
+      <c r="H162" s="9" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="9" t="n">
@@ -10929,25 +10433,25 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>External fan speed dutypercentage</t>
+          <t>L1-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>0x120C</t>
-        </is>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1220</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr"/>
       <c r="E163" s="9" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr"/>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
           <t>RO</t>
@@ -10961,25 +10465,25 @@
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>Q (Reference Output reactivepower)</t>
+          <t>L2-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>0x1226</t>
-        </is>
-      </c>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1221</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr"/>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr"/>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
           <t>RO</t>
@@ -10993,27 +10497,23 @@
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>L1 watt of grid</t>
+          <t>L3-N phase voltage (AC)</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>0x1300</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1222</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr"/>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
@@ -11029,27 +10529,23 @@
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>L2 watt of grid</t>
+          <t>L1-L2 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>0x1302</t>
-        </is>
-      </c>
-      <c r="D166" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1223</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr"/>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
@@ -11065,27 +10561,23 @@
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>L3 watt of grid</t>
+          <t>L2-L3 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>0x1304</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1224</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr"/>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>W 0.1</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
@@ -11101,27 +10593,23 @@
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>Accumulated energy ofimport</t>
+          <t>L3-L1 phase voltage (AC)</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>0x1306</t>
-        </is>
-      </c>
-      <c r="D168" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1225</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr"/>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
@@ -11129,11 +10617,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H168" s="9" t="inlineStr">
-        <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
+      <c r="H168" s="9" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="9" t="n">
@@ -11141,27 +10625,23 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Accumulated energy ofexport</t>
+          <t>Q (Reference Output reactive power)</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>0x1308</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1226</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr"/>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
@@ -11169,11 +10649,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H169" s="9" t="inlineStr">
-        <is>
-          <t>cumulative_energy</t>
-        </is>
-      </c>
+      <c r="H169" s="9" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="9" t="n">
@@ -11181,22 +10657,18 @@
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>L1 watt of load</t>
+          <t>L1 watt of grid</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>0x130A</t>
-        </is>
-      </c>
-      <c r="D170" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1300</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr"/>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
@@ -11217,22 +10689,18 @@
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>L2 watt of load</t>
+          <t>L2 watt of grid</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>0x130C</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1302</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr"/>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
@@ -11253,22 +10721,18 @@
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>L3 watt of load</t>
+          <t>L3 watt of grid</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>0x130E</t>
-        </is>
-      </c>
-      <c r="D172" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1304</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr"/>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
@@ -11289,19 +10753,15 @@
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Accumulated energy of load</t>
+          <t>Accumulated energy of import</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>0x1310</t>
-        </is>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1306</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr"/>
       <c r="E173" s="9" t="inlineStr">
         <is>
           <t>U32</t>
@@ -11329,27 +10789,23 @@
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>L1-N phase voltage of grid</t>
+          <t>Accumulated energy of export</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>0x131A</t>
-        </is>
-      </c>
-      <c r="D174" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1308</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr"/>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
@@ -11357,7 +10813,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H174" s="9" t="inlineStr"/>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="n">
@@ -11365,27 +10825,23 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>L2-N phase voltage of grid</t>
+          <t>L1 watt of load</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>0x131B</t>
-        </is>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x130A</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr"/>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
@@ -11401,27 +10857,23 @@
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>L3-N phase voltage of grid</t>
+          <t>L2 watt of load</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>0x131C</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x130C</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr"/>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
@@ -11437,27 +10889,23 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>L1 current of grid</t>
+          <t>L3 watt of load</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>0x131D</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x130E</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr"/>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W 0.1</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
@@ -11473,27 +10921,23 @@
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>L2 current of grid</t>
+          <t>Accumulated energy of load</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>0x131F</t>
-        </is>
-      </c>
-      <c r="D178" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1310</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr"/>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
@@ -11501,7 +10945,11 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H178" s="9" t="inlineStr"/>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>cumulative_energy</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="9" t="n">
@@ -11509,27 +10957,23 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>L3 current of grid</t>
+          <t>L1-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>0x1321</t>
-        </is>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x131A</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr"/>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
@@ -11545,19 +10989,15 @@
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>L1-N phase voltage of load</t>
+          <t>L2-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>0x1323</t>
-        </is>
-      </c>
-      <c r="D180" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x131B</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr"/>
       <c r="E180" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -11581,19 +11021,15 @@
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>L2-N phase voltage of load</t>
+          <t>L3-N phase voltage of grid</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>0x1324</t>
-        </is>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x131C</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr"/>
       <c r="E181" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -11617,27 +11053,23 @@
       </c>
       <c r="B182" s="9" t="inlineStr">
         <is>
-          <t>L3-N phase voltage of load</t>
+          <t>L1 current of grid</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
         <is>
-          <t>0x1325</t>
-        </is>
-      </c>
-      <c r="D182" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x131D</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr"/>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
@@ -11653,19 +11085,15 @@
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>L1 current of load</t>
+          <t>L2 current of grid</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>0x1326</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x131F</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr"/>
       <c r="E183" s="9" t="inlineStr">
         <is>
           <t>S32</t>
@@ -11689,19 +11117,15 @@
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>L2 current of load</t>
+          <t>L3 current of grid</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>0x1328</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1321</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr"/>
       <c r="E184" s="9" t="inlineStr">
         <is>
           <t>S32</t>
@@ -11725,27 +11149,23 @@
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>L3 current of load</t>
+          <t>L1-N phase voltage of load</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>0x132A</t>
-        </is>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1323</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr"/>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
@@ -11761,27 +11181,23 @@
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>Today import Energy</t>
+          <t>L2-N phase voltage of load</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>0x1332</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1324</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr"/>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -11797,27 +11213,23 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>Today export Energy</t>
+          <t>L3-N phase voltage of load</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>0x1334</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1325</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr"/>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>V 0.1</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
@@ -11833,27 +11245,23 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>Today load Energy</t>
+          <t>L1 current of load</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>0x1336</t>
-        </is>
-      </c>
-      <c r="D188" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1326</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr"/>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>U32</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>Wh 10</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
@@ -11869,27 +11277,23 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>Frequency of grid</t>
+          <t>L2 current of load</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>0x1338</t>
-        </is>
-      </c>
-      <c r="D189" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1328</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr"/>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Hz 0.01</t>
+          <t>A 0.01</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
@@ -11905,28 +11309,28 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>Power flow direction</t>
+          <t>L3 current of load</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>0x30B2</t>
-        </is>
-      </c>
-      <c r="D190" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x132A</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr"/>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F190" s="9" t="inlineStr"/>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr"/>
@@ -11937,28 +11341,28 @@
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>Maximum feed in grid power</t>
+          <t>Today import Energy</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>0x30B9</t>
-        </is>
-      </c>
-      <c r="D191" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1332</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr"/>
       <c r="E191" s="9" t="inlineStr">
         <is>
           <t>U32</t>
         </is>
       </c>
-      <c r="F191" s="9" t="inlineStr"/>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>Wh 10</t>
+        </is>
+      </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr"/>
@@ -11969,28 +11373,28 @@
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>Clear the EEPROM historyenergy record</t>
+          <t>Today export Energy</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>0x6009</t>
-        </is>
-      </c>
-      <c r="D192" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1334</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr"/>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
-        </is>
-      </c>
-      <c r="F192" s="9" t="inlineStr"/>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>Wh 10</t>
+        </is>
+      </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H192" s="9" t="inlineStr"/>
@@ -12001,27 +11405,23 @@
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>Tracker 1 voltage</t>
+          <t>Today load Energy</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>0x8000</t>
-        </is>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1336</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr"/>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>V 0.1</t>
+          <t>Wh 10</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
@@ -12037,27 +11437,23 @@
       </c>
       <c r="B194" s="9" t="inlineStr">
         <is>
-          <t>String 1-1 current</t>
+          <t>Frequency of grid</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>0x8040</t>
-        </is>
-      </c>
-      <c r="D194" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x1338</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr"/>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>Hz 0.01</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
@@ -12065,11 +11461,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="H194" s="9" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+      <c r="H194" s="9" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="n">
@@ -12077,39 +11469,27 @@
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>String 1-2 current</t>
+          <t>Power flow direction</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
         <is>
-          <t>0x8080</t>
-        </is>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x30B2</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr"/>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="F195" s="9" t="inlineStr">
-        <is>
-          <t>A 0.01</t>
-        </is>
-      </c>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F195" s="9" t="inlineStr"/>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H195" s="9" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="H195" s="9" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="9" t="n">
@@ -12117,39 +11497,31 @@
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>String 1-3 current</t>
+          <t>Maximum feed in grid power</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>0x80C0</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x30B9</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr"/>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>U32</t>
         </is>
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>A 0.01</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H196" s="9" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="9" t="n">
@@ -12157,39 +11529,27 @@
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>String 1-4 current</t>
+          <t>Clear the EEPROM history energy record</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>0x8100</t>
-        </is>
-      </c>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x6009</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr"/>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
-        </is>
-      </c>
-      <c r="F197" s="9" t="inlineStr">
-        <is>
-          <t>A 0.01</t>
-        </is>
-      </c>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F197" s="9" t="inlineStr"/>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H197" s="9" t="inlineStr">
-        <is>
-          <t>string_current</t>
-        </is>
-      </c>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="H197" s="9" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="9" t="n">
@@ -12197,19 +11557,15 @@
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>Tracker 2 voltage</t>
+          <t>Tracker 1 voltage</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>0x8140</t>
-        </is>
-      </c>
-      <c r="D198" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8000</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr"/>
       <c r="E198" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -12233,22 +11589,18 @@
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>String 2-1 current</t>
+          <t>String 1-1 current</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>0x8180</t>
-        </is>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8040</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr"/>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr">
@@ -12273,22 +11625,18 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>String 2-2 current</t>
+          <t>String 1-2 current</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>0x81C0</t>
-        </is>
-      </c>
-      <c r="D200" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8080</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr"/>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F200" s="9" t="inlineStr">
@@ -12313,22 +11661,18 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>String 2-3 current</t>
+          <t>String 1-3 current</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>0x8200</t>
-        </is>
-      </c>
-      <c r="D201" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x80C0</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="inlineStr"/>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F201" s="9" t="inlineStr">
@@ -12353,22 +11697,18 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>String 2-4 current</t>
+          <t>String 1-4 current</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>0x8240</t>
-        </is>
-      </c>
-      <c r="D202" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8100</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr"/>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
@@ -12393,19 +11733,15 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>Tracker 3 voltage</t>
+          <t>Tracker 2 voltage</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>0x8280</t>
-        </is>
-      </c>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8140</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr"/>
       <c r="E203" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -12429,22 +11765,18 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>String 3-1 current</t>
+          <t>String 2-1 current</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>0x82C0</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8180</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr"/>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr">
@@ -12469,22 +11801,18 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>String 3-2 current</t>
+          <t>String 2-2 current</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>0x8300</t>
-        </is>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x81C0</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr"/>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
@@ -12509,22 +11837,18 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>String 3-3 current</t>
+          <t>String 2-3 current</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>0x8340</t>
-        </is>
-      </c>
-      <c r="D206" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8200</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr"/>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F206" s="9" t="inlineStr">
@@ -12549,22 +11873,18 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>String 3-4 current</t>
+          <t>String 2-4 current</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>0x8380</t>
-        </is>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8240</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr"/>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
@@ -12589,19 +11909,15 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>Tracker 4 voltage</t>
+          <t>Tracker 3 voltage</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>0x83C0</t>
-        </is>
-      </c>
-      <c r="D208" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8280</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr"/>
       <c r="E208" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -12625,22 +11941,18 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>String 4-1 current</t>
+          <t>String 3-1 current</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>0x8400</t>
-        </is>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x82C0</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr"/>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
@@ -12665,22 +11977,18 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>String 4-2 current</t>
+          <t>String 3-2 current</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>0x8440</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8300</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr"/>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
@@ -12705,22 +12013,18 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>String 4-3 current</t>
+          <t>String 3-3 current</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>0x8480</t>
-        </is>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8340</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr"/>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
@@ -12745,22 +12049,18 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>String 4-4 current</t>
+          <t>String 3-4 current</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>0x84C0</t>
-        </is>
-      </c>
-      <c r="D212" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8380</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr"/>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
@@ -12785,19 +12085,15 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>Tracker 5 voltage</t>
+          <t>Tracker 4 voltage</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>0x8500</t>
-        </is>
-      </c>
-      <c r="D213" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x83C0</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr"/>
       <c r="E213" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -12821,22 +12117,18 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>String 5-1 current</t>
+          <t>String 4-1 current</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>0x8540</t>
-        </is>
-      </c>
-      <c r="D214" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8400</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr"/>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
@@ -12861,22 +12153,18 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>String 5-2 current</t>
+          <t>String 4-2 current</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>0x8580</t>
-        </is>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8440</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr"/>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
@@ -12901,22 +12189,18 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>String 5-3 current</t>
+          <t>String 4-3 current</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>0x85C0</t>
-        </is>
-      </c>
-      <c r="D216" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8480</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr"/>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
@@ -12941,22 +12225,18 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>String 5-4 current</t>
+          <t>String 4-4 current</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>0x8600</t>
-        </is>
-      </c>
-      <c r="D217" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x84C0</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr"/>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
@@ -12981,19 +12261,15 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>Tracker 6 voltage</t>
+          <t>Tracker 5 voltage</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>0x8640</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8500</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr"/>
       <c r="E218" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -13017,22 +12293,18 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>String 6-1 current</t>
+          <t>String 5-1 current</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>0x8680</t>
-        </is>
-      </c>
-      <c r="D219" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8540</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr"/>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -13057,22 +12329,18 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>String 6-2 current</t>
+          <t>String 5-2 current</t>
         </is>
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>0x86C0</t>
-        </is>
-      </c>
-      <c r="D220" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8580</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr"/>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
@@ -13097,22 +12365,18 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>String 6-3 current</t>
+          <t>String 5-3 current</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>0x8700</t>
-        </is>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x85C0</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr"/>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -13137,22 +12401,18 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>String 6-4 current</t>
+          <t>String 5-4 current</t>
         </is>
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>0x8740</t>
-        </is>
-      </c>
-      <c r="D222" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8600</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr"/>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
@@ -13177,19 +12437,15 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>Tracker 7 voltage</t>
+          <t>Tracker 6 voltage</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>0x8780</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8640</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr"/>
       <c r="E223" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -13213,22 +12469,18 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>String 7-1 current</t>
+          <t>String 6-1 current</t>
         </is>
       </c>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>0x87C0</t>
-        </is>
-      </c>
-      <c r="D224" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8680</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr"/>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
@@ -13253,22 +12505,18 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>String 7-2 current</t>
+          <t>String 6-2 current</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>0x8800</t>
-        </is>
-      </c>
-      <c r="D225" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x86C0</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr"/>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
@@ -13293,22 +12541,18 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>String 7-3 current</t>
+          <t>String 6-3 current</t>
         </is>
       </c>
       <c r="C226" s="9" t="inlineStr">
         <is>
-          <t>0x8840</t>
-        </is>
-      </c>
-      <c r="D226" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8700</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr"/>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
@@ -13333,22 +12577,18 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>String 7-4 current</t>
+          <t>String 6-4 current</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>0x8880</t>
-        </is>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8740</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr"/>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
@@ -13373,19 +12613,15 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>Tracker 8 voltage</t>
+          <t>Tracker 7 voltage</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t>0x88C0</t>
-        </is>
-      </c>
-      <c r="D228" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8780</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -13409,22 +12645,18 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>String 8-1 current</t>
+          <t>String 7-1 current</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>0x8900</t>
-        </is>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x87C0</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
@@ -13449,22 +12681,18 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>String 8-2 current</t>
+          <t>String 7-2 current</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t>0x8940</t>
-        </is>
-      </c>
-      <c r="D230" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8800</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
@@ -13489,22 +12717,18 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>String 8-3 current</t>
+          <t>String 7-3 current</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>0x8980</t>
-        </is>
-      </c>
-      <c r="D231" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8840</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr"/>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
@@ -13529,22 +12753,18 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>String 8-4 current</t>
+          <t>String 7-4 current</t>
         </is>
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>0x89C0</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8880</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr"/>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
@@ -13569,19 +12789,15 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>Tracker 9 voltage</t>
+          <t>Tracker 8 voltage</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>0x8A00</t>
-        </is>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x88C0</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr"/>
       <c r="E233" s="9" t="inlineStr">
         <is>
           <t>U16</t>
@@ -13605,22 +12821,18 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>String 9-1 current</t>
+          <t>String 8-1 current</t>
         </is>
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>0x8A40</t>
-        </is>
-      </c>
-      <c r="D234" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8900</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr"/>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
@@ -13645,22 +12857,18 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>String 9-2 current</t>
+          <t>String 8-2 current</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>0x8A80</t>
-        </is>
-      </c>
-      <c r="D235" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8940</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr"/>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
@@ -13685,22 +12893,18 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>String 9-3 current</t>
+          <t>String 8-3 current</t>
         </is>
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>0x8AC0</t>
-        </is>
-      </c>
-      <c r="D236" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8980</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr"/>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
@@ -13725,22 +12929,18 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>String 9-4 current</t>
+          <t>String 8-4 current</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t>0x8B00</t>
-        </is>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x89C0</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr"/>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>STRINGING</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
@@ -13765,25 +12965,25 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>history log 0</t>
+          <t>Tracker 9 voltage</t>
         </is>
       </c>
       <c r="C238" s="9" t="inlineStr">
         <is>
-          <t>0xB600</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>0x8A00</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr"/>
       <c r="E238" s="9" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr"/>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>V 0.1</t>
+        </is>
+      </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
           <t>RO</t>
@@ -13797,31 +12997,199 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
+          <t>String 9-1 current</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>0x8A40</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr"/>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="n">
+        <v>181</v>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>String 9-2 current</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>0x8A80</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr"/>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H240" s="9" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>String 9-3 current</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>0x8AC0</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr"/>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>String 9-4 current</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>0x8B00</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr"/>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>A 0.01</t>
+        </is>
+      </c>
+      <c r="G242" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H242" s="9" t="inlineStr">
+        <is>
+          <t>string_current</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>history log 0</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>0xB600</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr"/>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="F243" s="9" t="inlineStr"/>
+      <c r="G243" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H243" s="9" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
+        <is>
           <t>history log 127</t>
         </is>
       </c>
-      <c r="C239" s="9" t="inlineStr">
+      <c r="C244" s="9" t="inlineStr">
         <is>
           <t>0xB77D</t>
         </is>
       </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="E239" s="9" t="inlineStr">
+      <c r="D244" s="9" t="inlineStr"/>
+      <c r="E244" s="9" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="F239" s="9" t="inlineStr"/>
-      <c r="G239" s="9" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="H239" s="9" t="inlineStr"/>
+      <c r="F244" s="9" t="inlineStr"/>
+      <c r="G244" s="9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="H244" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
